--- a/data/trans_dic/IP15-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP15-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..)</t>
+          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,56; 32,84</t>
+          <t>14,31; 31,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,17; 39,06</t>
+          <t>18,2; 38,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,27; 38,06</t>
+          <t>19,43; 38,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,32; 57,25</t>
+          <t>29,37; 56,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,87; 29,32</t>
+          <t>12,87; 29,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,18; 39,47</t>
+          <t>20,32; 39,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,87; 40,07</t>
+          <t>21,12; 40,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,46; 38,68</t>
+          <t>20,33; 38,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,16; 27,86</t>
+          <t>15,55; 27,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,35; 35,48</t>
+          <t>21,68; 35,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,11; 36,26</t>
+          <t>22,51; 36,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,73; 44,39</t>
+          <t>27,43; 45,24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,51; 22,69</t>
+          <t>11,31; 22,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,44; 29,17</t>
+          <t>16,43; 29,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,5; 34,06</t>
+          <t>19,0; 33,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,19; 78,7</t>
+          <t>34,97; 74,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,87; 24,6</t>
+          <t>12,3; 24,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,34; 28,74</t>
+          <t>16,82; 29,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,63; 24,83</t>
+          <t>13,15; 24,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,49; 46,99</t>
+          <t>29,47; 46,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,36; 22,0</t>
+          <t>13,64; 21,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,91; 27,68</t>
+          <t>17,87; 27,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,16; 27,17</t>
+          <t>18,18; 27,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,84; 62,02</t>
+          <t>35,47; 62,34</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,93; 26,28</t>
+          <t>10,79; 25,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,93; 31,19</t>
+          <t>15,17; 31,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,44; 22,98</t>
+          <t>8,37; 23,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,43; 40,46</t>
+          <t>22,61; 42,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,25; 22,29</t>
+          <t>9,69; 22,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,62; 40,45</t>
+          <t>22,77; 41,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 19,13</t>
+          <t>6,84; 19,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,81; 39,82</t>
+          <t>21,02; 39,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,54; 21,75</t>
+          <t>11,66; 21,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,84; 33,89</t>
+          <t>20,96; 33,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,96; 19,14</t>
+          <t>8,99; 18,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,45; 37,22</t>
+          <t>23,79; 37,19</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,18; 31,29</t>
+          <t>14,95; 29,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,1; 33,05</t>
+          <t>17,19; 33,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,01; 40,28</t>
+          <t>22,42; 40,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,84; 28,37</t>
+          <t>11,21; 28,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,05; 29,47</t>
+          <t>13,93; 28,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,81; 26,22</t>
+          <t>11,67; 27,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,47; 40,92</t>
+          <t>23,47; 41,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,75; 23,44</t>
+          <t>7,06; 23,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,78; 26,72</t>
+          <t>16,03; 27,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,63; 27,52</t>
+          <t>16,78; 27,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,71; 37,87</t>
+          <t>24,73; 37,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,99; 23,38</t>
+          <t>10,33; 22,45</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,76; 33,5</t>
+          <t>12,82; 34,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,0; 45,55</t>
+          <t>22,52; 47,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,3; 26,73</t>
+          <t>7,55; 26,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,35; 35,24</t>
+          <t>14,99; 36,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,72; 29,09</t>
+          <t>9,3; 29,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,06; 38,51</t>
+          <t>16,56; 38,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 20,21</t>
+          <t>5,23; 20,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,43; 40,48</t>
+          <t>15,52; 39,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,85; 26,86</t>
+          <t>13,45; 27,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,6; 38,86</t>
+          <t>21,78; 37,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,8; 20,08</t>
+          <t>7,8; 19,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,48; 35,0</t>
+          <t>18,66; 33,92</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,71; 32,22</t>
+          <t>13,62; 31,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,88; 29,8</t>
+          <t>11,5; 29,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,3; 25,69</t>
+          <t>9,83; 26,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,24; 25,56</t>
+          <t>9,47; 26,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,64; 25,27</t>
+          <t>10,65; 26,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,89; 40,89</t>
+          <t>20,5; 40,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,08; 24,11</t>
+          <t>7,35; 25,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,77; 34,08</t>
+          <t>16,17; 34,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,65; 26,27</t>
+          <t>14,38; 26,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,99; 32,07</t>
+          <t>18,83; 31,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,94; 22,42</t>
+          <t>10,13; 22,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,04; 27,6</t>
+          <t>15,02; 27,83</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,88; 22,32</t>
+          <t>11,9; 23,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,47; 25,44</t>
+          <t>14,12; 25,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,78; 15,12</t>
+          <t>6,61; 14,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,85; 31,16</t>
+          <t>18,36; 31,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,53; 25,91</t>
+          <t>14,24; 25,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,78; 23,43</t>
+          <t>12,84; 23,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,18; 10,82</t>
+          <t>4,37; 11,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,52; 37,22</t>
+          <t>21,59; 37,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,47; 22,44</t>
+          <t>14,7; 22,2</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,51; 22,53</t>
+          <t>14,78; 22,43</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,63; 11,86</t>
+          <t>6,35; 11,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,6; 32,09</t>
+          <t>21,27; 31,61</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,15; 21,68</t>
+          <t>12,22; 21,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,12; 17,59</t>
+          <t>9,0; 17,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,14; 17,34</t>
+          <t>9,51; 17,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,35; 10,24</t>
+          <t>3,4; 10,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,18; 29,24</t>
+          <t>19,11; 29,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,05; 17,79</t>
+          <t>9,27; 17,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,91; 19,35</t>
+          <t>10,75; 19,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,58; 12,15</t>
+          <t>4,41; 12,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,88; 23,9</t>
+          <t>16,91; 24,44</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,1; 16,38</t>
+          <t>9,92; 16,05</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,91; 16,83</t>
+          <t>11,12; 16,71</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,77; 9,85</t>
+          <t>4,6; 9,47</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,07; 20,79</t>
+          <t>16,3; 20,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,26; 23,23</t>
+          <t>18,31; 23,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,72; 20,56</t>
+          <t>15,78; 20,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22,39; 37,97</t>
+          <t>22,44; 38,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,63; 22,56</t>
+          <t>17,64; 22,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,59; 23,46</t>
+          <t>18,66; 23,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,34; 18,82</t>
+          <t>14,4; 19,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20,87; 26,87</t>
+          <t>21,35; 27,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17,66; 20,86</t>
+          <t>17,47; 20,84</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,17; 22,72</t>
+          <t>19,25; 22,7</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15,61; 18,91</t>
+          <t>15,79; 18,86</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22,74; 31,08</t>
+          <t>22,75; 30,58</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>11668</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16092</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16092</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>30384</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18631</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>19206</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>22322</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>23803</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>34723</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>35298</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>52706</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>7523; 16706</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10454; 22011</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11145; 22061</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21524; 41410</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7749; 17879</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>13167; 25704</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>13614; 25891</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>16133; 30199</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>17543; 31524</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>26500; 43324</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>27427; 44020</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>41874; 69051</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>16730</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23483</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27263</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>63054</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>24976</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20682</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>48163</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>36586</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>48459</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>47945</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>111217</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>11484; 23005</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17203; 31284</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19751; 34550</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>43131; 92483</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>13372; 26826</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>18697; 33308</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>14498; 27119</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>37603; 59920</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>28691; 45760</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>38585; 58969</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>38946; 58349</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>89002; 156422</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>11627</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15530</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9523</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17941</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>22309</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>8339</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>20287</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>22188</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>37839</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>17862</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>38227</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>7294; 17443</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10342; 21772</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5595; 15739</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>13172; 24506</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6812; 15634</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>16224; 29770</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4785; 13384</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>14120; 26539</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>16083; 29664</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>29231; 46806</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>12295; 25708</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>29843; 46652</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>16351</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19319</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23799</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12520</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15242</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>25580</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>11072</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>32777</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>34561</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>49379</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>23593</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>11188; 22414</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>13370; 25994</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>17258; 30978</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>7862; 19729</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>11021; 22918</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>9596; 22212</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>19050; 33453</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>5515; 18637</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>24678; 42370</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>26853; 44243</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>39104; 59107</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>15319; 33289</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>9126</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14507</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6511</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8237</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>12287</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>10689</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>16947</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>26795</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>11679</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>18926</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>5367; 14396</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9887; 20768</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3280; 11371</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5172; 12466</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4172; 13050</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7743; 18117</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2422; 9339</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>6318; 16162</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>11663; 23805</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>19747; 34389</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>7004; 17281</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>14036; 25517</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>12379</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10988</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7679</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>18093</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>8685</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>13607</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>23108</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>29081</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>17790</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>21287</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>7633; 17928</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>6438; 16424</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>5333; 14381</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>4371; 12038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>6363; 15899</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>12351; 24243</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>4247; 14766</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>9088; 19217</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>16654; 30660</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>21885; 36733</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>11348; 24923</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>15376; 28486</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>21499</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>26559</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>14250</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>29786</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>25345</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>10604</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>44354</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>48025</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>51904</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>24854</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>74140</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>15304; 29680</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>19593; 35308</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>9082; 20461</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>22859; 38782</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>19324; 35021</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>18714; 33812</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>6298; 16221</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>33681; 58049</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>38839; 58665</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>42037; 63797</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>17880; 33333</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>59677; 88686</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>25924</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>21223</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>20919</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>8113</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>21692</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>25012</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>11707</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>65790</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>42915</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>45931</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>19819</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>19293; 33785</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>14821; 28144</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>15609; 28905</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>4470; 13177</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>31359; 48897</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>15742; 29434</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>18374; 33644</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>6886; 18745</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>54439; 78695</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>33195; 53680</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>37259; 55980</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>13232; 27259</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>125305</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>147701</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>127461</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>177715</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>182201</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>269224</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>306275</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>250737</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>359916</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>110980; 142532</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>130280; 167322</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>111129; 144884</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>148523; 256457</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>127498; 161419</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>140344; 177591</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>107274; 142274</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>162543; 206332</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>245290; 292494</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>281654; 332147</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>228851; 273319</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>323800; 435188</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP15-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP15-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,31; 31,78</t>
+          <t>14,18; 32,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,2; 38,33</t>
+          <t>20,23; 39,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,43; 38,45</t>
+          <t>18,97; 37,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,37; 56,51</t>
+          <t>29,55; 56,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,87; 29,69</t>
+          <t>12,79; 29,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,32; 39,66</t>
+          <t>20,4; 39,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,12; 40,16</t>
+          <t>19,71; 38,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,33; 38,05</t>
+          <t>19,73; 37,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,55; 27,95</t>
+          <t>15,73; 28,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,68; 35,44</t>
+          <t>21,95; 36,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,51; 36,13</t>
+          <t>22,89; 35,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,43; 45,24</t>
+          <t>26,91; 44,12</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,31; 22,65</t>
+          <t>11,08; 22,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,43; 29,88</t>
+          <t>16,77; 29,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,0; 33,24</t>
+          <t>19,27; 33,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,97; 74,98</t>
+          <t>34,36; 73,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,3; 24,67</t>
+          <t>12,66; 24,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,82; 29,96</t>
+          <t>16,32; 29,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,15; 24,59</t>
+          <t>13,36; 25,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,47; 46,96</t>
+          <t>28,5; 45,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,64; 21,76</t>
+          <t>13,72; 22,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,87; 27,32</t>
+          <t>18,17; 27,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,18; 27,24</t>
+          <t>18,02; 27,01</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,47; 62,34</t>
+          <t>35,43; 63,09</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,79; 25,8</t>
+          <t>10,63; 27,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,17; 31,93</t>
+          <t>14,57; 31,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,37; 23,55</t>
+          <t>8,65; 22,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,61; 42,06</t>
+          <t>21,92; 40,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,69; 22,23</t>
+          <t>8,93; 22,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,77; 41,78</t>
+          <t>23,2; 42,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,84; 19,15</t>
+          <t>6,73; 19,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,02; 39,51</t>
+          <t>21,25; 39,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,66; 21,51</t>
+          <t>11,3; 21,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,96; 33,57</t>
+          <t>21,27; 33,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,99; 18,8</t>
+          <t>8,64; 18,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,79; 37,19</t>
+          <t>24,37; 38,09</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,95; 29,94</t>
+          <t>14,13; 30,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,19; 33,43</t>
+          <t>17,63; 33,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,42; 40,25</t>
+          <t>22,72; 40,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,21; 28,13</t>
+          <t>10,49; 26,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,93; 28,97</t>
+          <t>13,85; 28,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,67; 27,01</t>
+          <t>11,89; 26,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,47; 41,21</t>
+          <t>23,15; 40,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 23,85</t>
+          <t>6,88; 25,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,03; 27,52</t>
+          <t>16,76; 26,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,78; 27,65</t>
+          <t>16,09; 27,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,73; 37,38</t>
+          <t>25,18; 37,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,33; 22,45</t>
+          <t>10,67; 22,29</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,82; 34,4</t>
+          <t>11,98; 32,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,52; 47,31</t>
+          <t>21,32; 45,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,55; 26,18</t>
+          <t>7,04; 25,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,99; 36,12</t>
+          <t>14,73; 35,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,3; 29,1</t>
+          <t>9,02; 27,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,56; 38,75</t>
+          <t>17,36; 37,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 20,15</t>
+          <t>5,12; 20,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,52; 39,69</t>
+          <t>15,58; 39,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,45; 27,46</t>
+          <t>12,95; 27,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,78; 37,93</t>
+          <t>21,57; 37,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,8; 19,25</t>
+          <t>7,77; 19,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,66; 33,92</t>
+          <t>17,61; 34,1</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,62; 31,98</t>
+          <t>14,21; 31,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,5; 29,34</t>
+          <t>12,0; 29,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,83; 26,5</t>
+          <t>10,0; 26,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,47; 26,07</t>
+          <t>9,47; 26,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,65; 26,62</t>
+          <t>10,74; 26,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,5; 40,24</t>
+          <t>20,83; 41,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,35; 25,57</t>
+          <t>8,03; 24,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,17; 34,2</t>
+          <t>15,83; 34,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,38; 26,48</t>
+          <t>14,53; 26,12</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,83; 31,6</t>
+          <t>19,26; 32,84</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,13; 22,25</t>
+          <t>10,69; 22,7</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,02; 27,83</t>
+          <t>15,33; 27,69</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,9; 23,08</t>
+          <t>11,82; 21,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,12; 25,45</t>
+          <t>13,66; 24,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,61; 14,89</t>
+          <t>6,88; 15,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,36; 31,15</t>
+          <t>17,49; 30,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,24; 25,82</t>
+          <t>13,99; 25,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,84; 23,2</t>
+          <t>12,34; 23,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 11,26</t>
+          <t>4,32; 11,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,59; 37,21</t>
+          <t>21,44; 38,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,7; 22,2</t>
+          <t>14,58; 22,15</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,78; 22,43</t>
+          <t>14,89; 22,56</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,35; 11,84</t>
+          <t>6,3; 11,92</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,27; 31,61</t>
+          <t>21,57; 31,64</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,22; 21,4</t>
+          <t>12,05; 21,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,0; 17,09</t>
+          <t>8,84; 17,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,51; 17,61</t>
+          <t>9,25; 17,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,4; 10,01</t>
+          <t>3,48; 10,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,11; 29,8</t>
+          <t>18,85; 29,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,27; 17,33</t>
+          <t>8,95; 17,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,75; 19,69</t>
+          <t>10,93; 19,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,41; 12,01</t>
+          <t>4,34; 11,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,91; 24,44</t>
+          <t>16,98; 23,78</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,92; 16,05</t>
+          <t>10,3; 16,2</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11,12; 16,71</t>
+          <t>10,8; 16,58</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,6; 9,47</t>
+          <t>4,85; 9,77</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,3; 20,93</t>
+          <t>16,22; 20,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,31; 23,52</t>
+          <t>18,36; 23,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,78; 20,57</t>
+          <t>15,79; 20,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22,44; 38,75</t>
+          <t>22,28; 37,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,64; 22,34</t>
+          <t>17,66; 22,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,66; 23,62</t>
+          <t>18,72; 23,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,4; 19,1</t>
+          <t>14,51; 19,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21,35; 27,1</t>
+          <t>21,02; 27,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17,47; 20,84</t>
+          <t>17,57; 20,92</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,25; 22,7</t>
+          <t>19,11; 22,64</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15,79; 18,86</t>
+          <t>15,71; 18,87</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22,75; 30,58</t>
+          <t>22,79; 29,94</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7523; 16706</t>
+          <t>7453; 16944</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10454; 22011</t>
+          <t>11618; 22817</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11145; 22061</t>
+          <t>10883; 21789</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21524; 41410</t>
+          <t>21653; 41126</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7749; 17879</t>
+          <t>7701; 17941</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13167; 25704</t>
+          <t>13223; 25813</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13614; 25891</t>
+          <t>12707; 24890</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16133; 30199</t>
+          <t>15658; 30078</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17543; 31524</t>
+          <t>17736; 32432</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26500; 43324</t>
+          <t>26836; 44286</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27427; 44020</t>
+          <t>27891; 43599</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41874; 69051</t>
+          <t>41078; 67354</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11484; 23005</t>
+          <t>11258; 23193</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17203; 31284</t>
+          <t>17564; 31390</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19751; 34550</t>
+          <t>20028; 34491</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43131; 92483</t>
+          <t>42375; 90057</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13372; 26826</t>
+          <t>13770; 27094</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18697; 33308</t>
+          <t>18140; 32588</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14498; 27119</t>
+          <t>14739; 28396</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37603; 59920</t>
+          <t>36365; 58381</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28691; 45760</t>
+          <t>28854; 46844</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38585; 58969</t>
+          <t>39225; 59734</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38946; 58349</t>
+          <t>38608; 57871</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>89002; 156422</t>
+          <t>88905; 158312</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7294; 17443</t>
+          <t>7184; 18287</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10342; 21772</t>
+          <t>9936; 21356</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5595; 15739</t>
+          <t>5779; 14920</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13172; 24506</t>
+          <t>12774; 23677</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6812; 15634</t>
+          <t>6279; 16142</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16224; 29770</t>
+          <t>16528; 30505</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4785; 13384</t>
+          <t>4702; 13400</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14120; 26539</t>
+          <t>14275; 26698</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16083; 29664</t>
+          <t>15582; 29690</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29231; 46806</t>
+          <t>29657; 46858</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12295; 25708</t>
+          <t>11811; 25131</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29843; 46652</t>
+          <t>30574; 47781</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11188; 22414</t>
+          <t>10579; 22668</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13370; 25994</t>
+          <t>13708; 26281</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17258; 30978</t>
+          <t>17488; 31053</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7862; 19729</t>
+          <t>7355; 18552</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11021; 22918</t>
+          <t>10954; 22656</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9596; 22212</t>
+          <t>9779; 21825</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19050; 33453</t>
+          <t>18794; 33163</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5515; 18637</t>
+          <t>5373; 19677</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24678; 42370</t>
+          <t>25800; 40962</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26853; 44243</t>
+          <t>25739; 43712</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39104; 59107</t>
+          <t>39825; 59772</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15319; 33289</t>
+          <t>15816; 33056</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5367; 14396</t>
+          <t>5014; 13718</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9887; 20768</t>
+          <t>9358; 20001</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3280; 11371</t>
+          <t>3057; 11225</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5172; 12466</t>
+          <t>5083; 12107</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4172; 13050</t>
+          <t>4047; 12435</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7743; 18117</t>
+          <t>8117; 17384</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2422; 9339</t>
+          <t>2375; 9403</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6318; 16162</t>
+          <t>6343; 16253</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11663; 23805</t>
+          <t>11228; 23721</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19747; 34389</t>
+          <t>19550; 34051</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7004; 17281</t>
+          <t>6973; 17641</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14036; 25517</t>
+          <t>13248; 25655</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7633; 17928</t>
+          <t>7963; 17774</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6438; 16424</t>
+          <t>6720; 16780</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5333; 14381</t>
+          <t>5428; 14364</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4371; 12038</t>
+          <t>4372; 12142</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6363; 15899</t>
+          <t>6418; 15913</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12351; 24243</t>
+          <t>12546; 24740</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4247; 14766</t>
+          <t>4636; 14176</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9088; 19217</t>
+          <t>8896; 19379</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16654; 30660</t>
+          <t>16826; 30242</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21885; 36733</t>
+          <t>22380; 38174</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11348; 24923</t>
+          <t>11972; 25421</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15376; 28486</t>
+          <t>15688; 28346</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>15304; 29680</t>
+          <t>15204; 27661</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19593; 35308</t>
+          <t>18950; 34573</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9082; 20461</t>
+          <t>9455; 21303</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22859; 38782</t>
+          <t>21780; 38520</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>19324; 35021</t>
+          <t>18984; 34829</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18714; 33812</t>
+          <t>17981; 33565</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6298; 16221</t>
+          <t>6227; 16198</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>33681; 58049</t>
+          <t>33448; 59864</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>38839; 58665</t>
+          <t>38538; 58547</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42037; 63797</t>
+          <t>42345; 64176</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17880; 33333</t>
+          <t>17718; 33548</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>59677; 88686</t>
+          <t>60495; 88763</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19293; 33785</t>
+          <t>19035; 33981</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14821; 28144</t>
+          <t>14559; 28239</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15609; 28905</t>
+          <t>15179; 28380</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4470; 13177</t>
+          <t>4587; 13446</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>31359; 48897</t>
+          <t>30923; 49095</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15742; 29434</t>
+          <t>15190; 29310</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18374; 33644</t>
+          <t>18671; 33170</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6886; 18745</t>
+          <t>6769; 17994</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>54439; 78695</t>
+          <t>54682; 76549</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>33195; 53680</t>
+          <t>34452; 54195</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>37259; 55980</t>
+          <t>36177; 55562</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>13232; 27259</t>
+          <t>13944; 28122</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>110980; 142532</t>
+          <t>110452; 142934</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>130280; 167322</t>
+          <t>130633; 166963</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>111129; 144884</t>
+          <t>111243; 143709</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>148523; 256457</t>
+          <t>147455; 245221</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>127498; 161419</t>
+          <t>127646; 162371</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>140344; 177591</t>
+          <t>140740; 177977</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>107274; 142274</t>
+          <t>108085; 141931</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>162543; 206332</t>
+          <t>160032; 206571</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>245290; 292494</t>
+          <t>246620; 293691</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>281654; 332147</t>
+          <t>279624; 331255</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>228851; 273319</t>
+          <t>227717; 273513</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>323800; 435188</t>
+          <t>324265; 426090</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP15-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP15-Provincia-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20,15%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28,75%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29,79%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30,05%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>22,2%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>28,02%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>28,05%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>41,46%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20,15%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>28,75%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,79%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,18; 32,23</t>
+          <t>12,87; 29,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,23; 39,73</t>
+          <t>20,18; 39,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,97; 37,98</t>
+          <t>20,87; 40,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,55; 56,12</t>
+          <t>21,82; 40,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,79; 29,79</t>
+          <t>14,56; 32,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,4; 39,83</t>
+          <t>18,17; 39,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,71; 38,61</t>
+          <t>19,27; 38,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,73; 37,9</t>
+          <t>27,66; 47,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,73; 28,76</t>
+          <t>15,16; 27,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,95; 36,23</t>
+          <t>21,35; 35,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,89; 35,79</t>
+          <t>22,11; 36,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,91; 44,12</t>
+          <t>26,77; 40,68</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18,26%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22,47%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18,75%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>36,83%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>16,47%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>22,43%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>26,23%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>51,12%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>18,26%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>22,47%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,75%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>37,79%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,08; 22,84</t>
+          <t>12,87; 24,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,77; 29,98</t>
+          <t>16,34; 28,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,27; 33,18</t>
+          <t>13,63; 24,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,36; 73,01</t>
+          <t>28,46; 46,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,66; 24,91</t>
+          <t>11,51; 22,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,32; 29,32</t>
+          <t>16,44; 29,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,36; 25,75</t>
+          <t>19,5; 34,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,5; 45,75</t>
+          <t>29,26; 47,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,72; 22,27</t>
+          <t>13,36; 22,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,17; 27,67</t>
+          <t>17,91; 27,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,02; 27,01</t>
+          <t>18,16; 27,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,43; 63,09</t>
+          <t>31,56; 43,66</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15,02%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>31,31%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11,93%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>29,77%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>17,2%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>22,78%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>14,25%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30,79%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15,02%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>31,31%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,93%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,63; 27,05</t>
+          <t>9,25; 22,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,57; 31,32</t>
+          <t>22,62; 40,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,65; 22,33</t>
+          <t>6,07; 19,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,92; 40,64</t>
+          <t>20,21; 39,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,93; 22,95</t>
+          <t>9,93; 26,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,2; 42,81</t>
+          <t>14,93; 31,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 19,17</t>
+          <t>8,44; 22,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,25; 39,75</t>
+          <t>22,09; 39,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,3; 21,53</t>
+          <t>11,54; 21,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,27; 33,61</t>
+          <t>20,84; 33,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,64; 18,38</t>
+          <t>8,96; 19,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,37; 38,09</t>
+          <t>24,03; 36,7</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20,76%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18,53%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>31,51%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14,43%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>21,84%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>24,84%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>30,92%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17,85%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20,76%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,53%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>31,51%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,13; 30,28</t>
+          <t>14,05; 29,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,63; 33,8</t>
+          <t>11,81; 26,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,72; 40,35</t>
+          <t>22,47; 40,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 26,45</t>
+          <t>7,07; 24,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,85; 28,64</t>
+          <t>15,18; 31,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,89; 26,54</t>
+          <t>17,1; 33,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,15; 40,85</t>
+          <t>23,01; 40,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 25,18</t>
+          <t>10,8; 28,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,76; 26,6</t>
+          <t>15,78; 26,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,09; 27,32</t>
+          <t>16,63; 27,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,18; 37,8</t>
+          <t>25,71; 37,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,67; 22,29</t>
+          <t>10,96; 23,56</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17,44%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>26,28%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>24,61%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>21,81%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>33,05%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>14,99%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>23,87%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>17,44%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>26,28%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,98; 32,78</t>
+          <t>9,72; 29,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,32; 45,56</t>
+          <t>17,06; 38,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,04; 25,84</t>
+          <t>5,02; 20,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,73; 35,08</t>
+          <t>15,5; 39,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,02; 27,73</t>
+          <t>12,76; 33,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,36; 37,18</t>
+          <t>21,0; 45,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,12; 20,29</t>
+          <t>7,3; 26,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,58; 39,91</t>
+          <t>14,17; 34,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,95; 27,36</t>
+          <t>12,85; 26,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,57; 37,56</t>
+          <t>22,6; 38,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,77; 19,65</t>
+          <t>7,8; 20,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,61; 34,1</t>
+          <t>17,67; 33,82</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17,96%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30,03%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23,37%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>22,08%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>19,63%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>16,78%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>16,63%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17,96%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>30,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,04%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,21; 31,71</t>
+          <t>10,64; 25,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,0; 29,97</t>
+          <t>20,89; 40,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,0; 26,47</t>
+          <t>8,08; 24,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,47; 26,3</t>
+          <t>15,9; 33,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,74; 26,64</t>
+          <t>14,71; 32,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,83; 41,07</t>
+          <t>11,88; 29,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,03; 24,55</t>
+          <t>9,3; 25,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,83; 34,49</t>
+          <t>9,46; 25,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,53; 26,12</t>
+          <t>14,65; 26,27</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,26; 32,84</t>
+          <t>18,99; 32,07</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,69; 22,7</t>
+          <t>10,94; 22,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,33; 27,69</t>
+          <t>14,44; 26,44</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>19,55%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17,39%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29,73%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>16,72%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>19,15%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>10,37%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>23,92%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>19,55%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,39%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,4%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,82; 21,51</t>
+          <t>14,53; 25,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,66; 24,92</t>
+          <t>12,78; 23,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,88; 15,51</t>
+          <t>4,18; 10,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,49; 30,94</t>
+          <t>22,96; 38,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,99; 25,67</t>
+          <t>11,88; 22,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,34; 23,03</t>
+          <t>14,47; 25,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,32; 11,24</t>
+          <t>6,78; 15,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,44; 38,37</t>
+          <t>18,74; 31,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,58; 22,15</t>
+          <t>14,47; 22,44</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,89; 22,56</t>
+          <t>14,51; 22,53</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,3; 11,92</t>
+          <t>6,63; 11,86</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,57; 31,64</t>
+          <t>22,54; 33,09</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>24,3%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>14,64%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>16,42%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>12,89%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>12,74%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>24,3%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>14,64%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,05; 21,52</t>
+          <t>19,18; 29,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,84; 17,14</t>
+          <t>9,05; 17,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,25; 17,29</t>
+          <t>10,91; 19,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,48; 10,22</t>
+          <t>4,56; 12,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,85; 29,93</t>
+          <t>12,15; 21,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,95; 17,26</t>
+          <t>9,12; 17,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,93; 19,41</t>
+          <t>9,14; 17,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,34; 11,53</t>
+          <t>2,91; 9,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,98; 23,78</t>
+          <t>16,88; 23,9</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,3; 16,2</t>
+          <t>10,1; 16,38</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,8; 16,58</t>
+          <t>10,91; 16,83</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,85; 9,77</t>
+          <t>4,49; 9,42</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>19,91%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>21,09%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>18,4%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>20,76%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>18,1%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>26,85%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>21,09%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>16,55%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,22; 20,99</t>
+          <t>17,63; 22,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,36; 23,47</t>
+          <t>18,59; 23,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,79; 20,4</t>
+          <t>14,34; 18,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22,28; 37,05</t>
+          <t>20,52; 26,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,66; 22,47</t>
+          <t>16,07; 20,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,72; 23,67</t>
+          <t>18,26; 23,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,51; 19,06</t>
+          <t>15,72; 20,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21,02; 27,14</t>
+          <t>19,99; 25,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17,57; 20,92</t>
+          <t>17,66; 20,86</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,11; 22,64</t>
+          <t>19,17; 22,72</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15,71; 18,87</t>
+          <t>15,61; 18,91</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22,79; 29,94</t>
+          <t>21,28; 25,44</t>
         </is>
       </c>
     </row>
@@ -1951,13 +1951,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18631</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19206</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19273</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>11668</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>16092</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>16092</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30384</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18631</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>19206</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>40073</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7453; 16944</t>
+          <t>7748; 17655</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11618; 22817</t>
+          <t>13080; 25580</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10883; 21789</t>
+          <t>13455; 25831</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21653; 41126</t>
+          <t>13998; 25817</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7701; 17941</t>
+          <t>7654; 17265</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13223; 25813</t>
+          <t>10437; 22432</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12707; 24890</t>
+          <t>11054; 21834</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15658; 30078</t>
+          <t>15621; 26715</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17736; 32432</t>
+          <t>17093; 31423</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26836; 44286</t>
+          <t>26102; 43371</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27891; 43599</t>
+          <t>26933; 44174</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41078; 67354</t>
+          <t>32286; 49072</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>55</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24976</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20682</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>42668</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>16730</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>23483</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>27263</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>63054</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>24976</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20682</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>38767</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>111217</t>
+          <t>81435</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11258; 23193</t>
+          <t>13996; 26749</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17564; 31390</t>
+          <t>18166; 31946</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20028; 34491</t>
+          <t>15033; 27386</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42375; 90057</t>
+          <t>32966; 53499</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13770; 27094</t>
+          <t>11694; 23047</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18140; 32588</t>
+          <t>17215; 30540</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14739; 28396</t>
+          <t>20268; 35408</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36365; 58381</t>
+          <t>29170; 47251</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28854; 46844</t>
+          <t>28106; 46263</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39225; 59734</t>
+          <t>38666; 59744</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38608; 57871</t>
+          <t>38910; 58203</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>88905; 158312</t>
+          <t>68011; 94103</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>22309</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8339</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17678</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>11627</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>15530</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>9523</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17941</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>22309</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>8339</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>34878</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7184; 18287</t>
+          <t>6507; 15673</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9936; 21356</t>
+          <t>16119; 28819</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5779; 14920</t>
+          <t>4246; 13370</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12774; 23677</t>
+          <t>12000; 23164</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6279; 16142</t>
+          <t>6712; 17763</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16528; 30505</t>
+          <t>10176; 21266</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4702; 13400</t>
+          <t>5643; 15355</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14275; 26698</t>
+          <t>12494; 22572</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15582; 29690</t>
+          <t>15912; 29997</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29657; 46858</t>
+          <t>29053; 47250</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11811; 25131</t>
+          <t>12255; 26178</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30574; 47781</t>
+          <t>27862; 42553</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15242</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25580</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10416</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>16351</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>19319</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>23799</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12520</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15242</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>25580</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>22639</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10579; 22668</t>
+          <t>11117; 23317</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13708; 26281</t>
+          <t>9715; 21564</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17488; 31053</t>
+          <t>18243; 33217</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7355; 18552</t>
+          <t>5104; 17444</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10954; 22656</t>
+          <t>11367; 23427</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9779; 21825</t>
+          <t>13299; 25698</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18794; 33163</t>
+          <t>17708; 31003</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5373; 19677</t>
+          <t>7650; 19849</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25800; 40962</t>
+          <t>24301; 41143</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25739; 43712</t>
+          <t>26610; 44027</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39825; 59772</t>
+          <t>40654; 59891</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15816; 33056</t>
+          <t>15673; 33691</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12287</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>9126</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>14507</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>6511</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8237</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>12287</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5168</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10689</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>18180</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5014; 13718</t>
+          <t>4361; 13044</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9358; 20001</t>
+          <t>7977; 18003</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3057; 11225</t>
+          <t>2329; 9366</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5083; 12107</t>
+          <t>6134; 15459</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4047; 12435</t>
+          <t>5342; 14019</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8117; 17384</t>
+          <t>9220; 19999</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2375; 9403</t>
+          <t>3170; 11612</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6343; 16253</t>
+          <t>5045; 12455</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11228; 23721</t>
+          <t>11140; 23285</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19550; 34051</t>
+          <t>20489; 35232</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6973; 17641</t>
+          <t>7006; 18027</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13248; 25655</t>
+          <t>13285; 25430</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>18093</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>8685</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>12379</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>10988</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>9105</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7679</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>18093</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>8685</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21287</t>
+          <t>19099</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7963; 17774</t>
+          <t>6357; 15092</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6720; 16780</t>
+          <t>12584; 24636</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5428; 14364</t>
+          <t>4664; 13923</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4372; 12142</t>
+          <t>7783; 16289</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6418; 15913</t>
+          <t>8244; 18060</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12546; 24740</t>
+          <t>6649; 16682</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4636; 14176</t>
+          <t>5046; 13945</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8896; 19379</t>
+          <t>4331; 11857</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16826; 30242</t>
+          <t>16959; 30423</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22380; 38174</t>
+          <t>22067; 37274</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11972; 25421</t>
+          <t>12250; 25108</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15688; 28346</t>
+          <t>13672; 25038</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>25345</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>10604</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>42033</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>21499</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>26559</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>14250</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>29786</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>25345</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>10604</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>44354</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>74140</t>
+          <t>72300</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>15204; 27661</t>
+          <t>19705; 35149</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18950; 34573</t>
+          <t>18630; 34141</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9455; 21303</t>
+          <t>6025; 15591</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21780; 38520</t>
+          <t>32458; 54030</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>18984; 34829</t>
+          <t>15280; 28704</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17981; 33565</t>
+          <t>20079; 35285</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6227; 16198</t>
+          <t>9316; 20765</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>33448; 59864</t>
+          <t>22958; 39063</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>38538; 58547</t>
+          <t>38240; 59307</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42345; 64176</t>
+          <t>41289; 64097</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17718; 33548</t>
+          <t>18669; 33375</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>60495; 88763</t>
+          <t>59472; 87327</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>21692</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>25012</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>11707</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>25924</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>21223</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>20919</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>8113</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>21692</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>25012</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>19341</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19035; 33981</t>
+          <t>31459; 47977</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14559; 28239</t>
+          <t>15375; 30210</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15179; 28380</t>
+          <t>18644; 33066</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4587; 13446</t>
+          <t>7244; 19504</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>30923; 49095</t>
+          <t>19178; 34236</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15190; 29310</t>
+          <t>15016; 28976</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18671; 33170</t>
+          <t>15001; 28468</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6769; 17994</t>
+          <t>4083; 12994</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>54682; 76549</t>
+          <t>54349; 76937</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>34452; 54195</t>
+          <t>33775; 54779</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>36177; 55562</t>
+          <t>36562; 56380</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>13944; 28122</t>
+          <t>13436; 28199</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>226</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>110452; 142934</t>
+          <t>127434; 163024</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>130633; 166963</t>
+          <t>139830; 176392</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>111243; 143709</t>
+          <t>106791; 140198</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>147455; 245221</t>
+          <t>143688; 185319</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>127646; 162371</t>
+          <t>109450; 141613</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>140740; 177977</t>
+          <t>129929; 165279</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>108085; 141931</t>
+          <t>110759; 144834</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>160032; 206571</t>
+          <t>125557; 161697</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>246620; 293691</t>
+          <t>247844; 292802</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>279624; 331255</t>
+          <t>280503; 332508</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>227717; 273513</t>
+          <t>226261; 274110</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>324265; 426090</t>
+          <t>282577; 337946</t>
         </is>
       </c>
     </row>
